--- a/FRA_WB_timeseries.xlsx
+++ b/FRA_WB_timeseries.xlsx
@@ -14,21 +14,105 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+  <si>
+    <t>Bank capital to assets ratio (%)</t>
+  </si>
+  <si>
+    <t>Bank nonperforming loans (% of gross loans)</t>
+  </si>
+  <si>
+    <t>Control of Corruption</t>
+  </si>
+  <si>
+    <t>Current account balance (% of GDP)</t>
+  </si>
+  <si>
+    <t>Domestic credit to private sector (% of GDP)</t>
+  </si>
+  <si>
+    <t>Exports of goods and services (% of GDP)</t>
+  </si>
   <si>
     <t>GDP growth (annual %)</t>
   </si>
   <si>
+    <t>GDP per capita (PPP, international $)</t>
+  </si>
+  <si>
+    <t>GDP per capita (current US$)</t>
+  </si>
+  <si>
+    <t>GDP per capita growth (annual %)</t>
+  </si>
+  <si>
+    <t>Gini index</t>
+  </si>
+  <si>
+    <t>Government Effectiveness</t>
+  </si>
+  <si>
+    <t>Government consumption (% of GDP)</t>
+  </si>
+  <si>
+    <t>Government expenditure (% of GDP)</t>
+  </si>
+  <si>
+    <t>Government revenue (% of GDP)</t>
+  </si>
+  <si>
+    <t>Imports of goods and services (% of GDP)</t>
+  </si>
+  <si>
     <t>Inflation, consumer prices (annual %)</t>
   </si>
   <si>
     <t>Interest payments (% of GDP)</t>
   </si>
   <si>
+    <t>Life expectancy at birth (years)</t>
+  </si>
+  <si>
+    <t>Military expenditure (% of GDP)</t>
+  </si>
+  <si>
+    <t>Net lending/borrowing (% of GDP)</t>
+  </si>
+  <si>
+    <t>Political Stability and Absence of Violence</t>
+  </si>
+  <si>
+    <t>Population, total</t>
+  </si>
+  <si>
+    <t>Poverty headcount ratio ($2.15/day)</t>
+  </si>
+  <si>
+    <t>Regulatory Quality</t>
+  </si>
+  <si>
+    <t>Rule of Law</t>
+  </si>
+  <si>
     <t>Tax revenue (% of GDP)</t>
   </si>
   <si>
+    <t>Total reserves (current US$)</t>
+  </si>
+  <si>
+    <t>Total reserves (months of imports)</t>
+  </si>
+  <si>
+    <t>Trade openness (% of GDP)</t>
+  </si>
+  <si>
     <t>Unemployment (% labor force)</t>
+  </si>
+  <si>
+    <t>Urban population (% of total)</t>
+  </si>
+  <si>
+    <t>Voice and Accountability</t>
   </si>
   <si>
     <t>date</t>
@@ -389,12 +473,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:AH26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:34">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -411,499 +495,2566 @@
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:34">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
-      <c r="B2">
+      <c r="D2">
+        <v>1.32172358036041</v>
+      </c>
+      <c r="E2">
+        <v>1.1848394944316</v>
+      </c>
+      <c r="G2">
+        <v>29.7580489893129</v>
+      </c>
+      <c r="H2">
         <v>4.14099996402915</v>
       </c>
-      <c r="C2">
+      <c r="I2">
+        <v>26001.8796983416</v>
+      </c>
+      <c r="J2">
+        <v>22340.5939516217</v>
+      </c>
+      <c r="K2">
+        <v>3.42869029655284</v>
+      </c>
+      <c r="L2">
+        <v>32.6</v>
+      </c>
+      <c r="M2">
+        <v>1.63705730438232</v>
+      </c>
+      <c r="N2">
+        <v>22.4026551978725</v>
+      </c>
+      <c r="O2">
+        <v>44.7395900950739</v>
+      </c>
+      <c r="P2">
+        <v>43.439130304069</v>
+      </c>
+      <c r="Q2">
+        <v>28.0279980425069</v>
+      </c>
+      <c r="R2">
         <v>1.67595988720928</v>
       </c>
-      <c r="D2">
+      <c r="S2">
         <v>6.18648042550455</v>
       </c>
-      <c r="E2">
+      <c r="T2">
+        <v>79.0560975609756</v>
+      </c>
+      <c r="U2">
+        <v>2.08501824480333</v>
+      </c>
+      <c r="V2">
+        <v>-1.38495150345368</v>
+      </c>
+      <c r="W2">
+        <v>0.785089075565338</v>
+      </c>
+      <c r="X2">
+        <v>60918661</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.914936780929565</v>
+      </c>
+      <c r="AA2">
+        <v>1.43230748176575</v>
+      </c>
+      <c r="AB2">
         <v>23.5306025928572</v>
       </c>
-      <c r="F2">
+      <c r="AC2">
+        <v>63728079967.5087</v>
+      </c>
+      <c r="AD2">
+        <v>1.74747387511078</v>
+      </c>
+      <c r="AE2">
+        <v>57.7860470318197</v>
+      </c>
+      <c r="AF2">
         <v>10.218</v>
       </c>
+      <c r="AG2">
+        <v>75.871</v>
+      </c>
+      <c r="AH2">
+        <v>1.18298661708832</v>
+      </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:34">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
-      <c r="B3">
+      <c r="E3">
+        <v>1.52989945223821</v>
+      </c>
+      <c r="F3">
+        <v>77.3883861486517</v>
+      </c>
+      <c r="G3">
+        <v>29.4306035099419</v>
+      </c>
+      <c r="H3">
         <v>1.89946701186636</v>
       </c>
-      <c r="C3">
+      <c r="I3">
+        <v>27349.7445859002</v>
+      </c>
+      <c r="J3">
+        <v>22331.7948343036</v>
+      </c>
+      <c r="K3">
+        <v>1.1593271284506</v>
+      </c>
+      <c r="L3">
+        <v>32.5</v>
+      </c>
+      <c r="N3">
+        <v>22.259556730345</v>
+      </c>
+      <c r="O3">
+        <v>45.1259611564405</v>
+      </c>
+      <c r="P3">
+        <v>43.8061268925512</v>
+      </c>
+      <c r="Q3">
+        <v>27.4626293461303</v>
+      </c>
+      <c r="R3">
         <v>1.63478079549602</v>
       </c>
-      <c r="D3">
+      <c r="S3">
         <v>6.13520683046877</v>
       </c>
-      <c r="E3">
+      <c r="T3">
+        <v>79.15853658536589</v>
+      </c>
+      <c r="U3">
+        <v>2.03069528996546</v>
+      </c>
+      <c r="V3">
+        <v>-1.46983384887589</v>
+      </c>
+      <c r="X3">
+        <v>61364377</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
         <v>23.563254487096</v>
       </c>
-      <c r="F3">
+      <c r="AC3">
+        <v>58637344263.961</v>
+      </c>
+      <c r="AD3">
+        <v>1.61505896061532</v>
+      </c>
+      <c r="AE3">
+        <v>56.8932328560722</v>
+      </c>
+      <c r="AF3">
         <v>8.609999999999999</v>
       </c>
+      <c r="AG3">
+        <v>76.127</v>
+      </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:34">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
-      <c r="B4">
+      <c r="D4">
+        <v>1.19158518314362</v>
+      </c>
+      <c r="E4">
+        <v>1.18270439802011</v>
+      </c>
+      <c r="F4">
+        <v>76.5284393068992</v>
+      </c>
+      <c r="G4">
+        <v>28.7307017592768</v>
+      </c>
+      <c r="H4">
         <v>1.06775027069419</v>
       </c>
-      <c r="C4">
+      <c r="I4">
+        <v>28350.0985605428</v>
+      </c>
+      <c r="J4">
+        <v>24144.5727019529</v>
+      </c>
+      <c r="K4">
+        <v>0.335619014023663</v>
+      </c>
+      <c r="L4">
+        <v>31.8</v>
+      </c>
+      <c r="M4">
+        <v>1.54408168792725</v>
+      </c>
+      <c r="N4">
+        <v>22.857888310331</v>
+      </c>
+      <c r="O4">
+        <v>46.1481322288413</v>
+      </c>
+      <c r="P4">
+        <v>43.1438246389983</v>
+      </c>
+      <c r="Q4">
+        <v>26.4018230910334</v>
+      </c>
+      <c r="R4">
         <v>1.9234122872706</v>
       </c>
-      <c r="D4">
+      <c r="S4">
         <v>6.03730246989854</v>
       </c>
-      <c r="E4">
+      <c r="T4">
+        <v>79.2609756097561</v>
+      </c>
+      <c r="U4">
+        <v>2.04625799037992</v>
+      </c>
+      <c r="V4">
+        <v>-3.25940626880151</v>
+      </c>
+      <c r="W4">
+        <v>0.924183249473572</v>
+      </c>
+      <c r="X4">
+        <v>61812142</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0.975888848304749</v>
+      </c>
+      <c r="AA4">
+        <v>1.21287262439728</v>
+      </c>
+      <c r="AB4">
         <v>22.764124672502</v>
       </c>
-      <c r="F4">
+      <c r="AC4">
+        <v>61696755317.4323</v>
+      </c>
+      <c r="AD4">
+        <v>1.62262317645235</v>
+      </c>
+      <c r="AE4">
+        <v>55.1325248503102</v>
+      </c>
+      <c r="AF4">
         <v>8.702</v>
       </c>
+      <c r="AG4">
+        <v>76.38</v>
+      </c>
+      <c r="AH4">
+        <v>1.15434229373932</v>
+      </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:34">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
-      <c r="B5">
+      <c r="D5">
+        <v>1.30575609207153</v>
+      </c>
+      <c r="E5">
+        <v>0.871063406872808</v>
+      </c>
+      <c r="F5">
+        <v>75.9612449584322</v>
+      </c>
+      <c r="G5">
+        <v>27.1369676673944</v>
+      </c>
+      <c r="H5">
         <v>0.967827182558352</v>
       </c>
-      <c r="C5">
+      <c r="I5">
+        <v>28027.6762119343</v>
+      </c>
+      <c r="J5">
+        <v>29479.5222101175</v>
+      </c>
+      <c r="K5">
+        <v>0.257866805308325</v>
+      </c>
+      <c r="L5">
+        <v>31.4</v>
+      </c>
+      <c r="M5">
+        <v>1.6510945558548</v>
+      </c>
+      <c r="N5">
+        <v>23.2625915298209</v>
+      </c>
+      <c r="O5">
+        <v>46.378152228103</v>
+      </c>
+      <c r="P5">
+        <v>42.548360587428</v>
+      </c>
+      <c r="Q5">
+        <v>25.4619146196714</v>
+      </c>
+      <c r="R5">
         <v>2.09847219146923</v>
       </c>
-      <c r="D5">
+      <c r="S5">
         <v>5.74095888257117</v>
       </c>
-      <c r="E5">
+      <c r="T5">
+        <v>79.1146341463415</v>
+      </c>
+      <c r="U5">
+        <v>2.0956804128006</v>
+      </c>
+      <c r="V5">
+        <v>-4.10090458510837</v>
+      </c>
+      <c r="W5">
+        <v>0.179551064968109</v>
+      </c>
+      <c r="X5">
+        <v>62249855</v>
+      </c>
+      <c r="Y5">
+        <v>0.2</v>
+      </c>
+      <c r="Z5">
+        <v>1.21546447277069</v>
+      </c>
+      <c r="AA5">
+        <v>1.33328890800476</v>
+      </c>
+      <c r="AB5">
         <v>22.2935305694438</v>
       </c>
-      <c r="F5">
+      <c r="AC5">
+        <v>70762382918.7419</v>
+      </c>
+      <c r="AD5">
+        <v>1.55732088735449</v>
+      </c>
+      <c r="AE5">
+        <v>52.5988822870657</v>
+      </c>
+      <c r="AF5">
         <v>8.305999999999999</v>
       </c>
+      <c r="AG5">
+        <v>76.63200000000001</v>
+      </c>
+      <c r="AH5">
+        <v>1.12266278266907</v>
+      </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:34">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
-      <c r="B6">
+      <c r="D6">
+        <v>1.31116378307343</v>
+      </c>
+      <c r="E6">
+        <v>0.434470120439983</v>
+      </c>
+      <c r="F6">
+        <v>76.97441618831159</v>
+      </c>
+      <c r="G6">
+        <v>27.5381038597962</v>
+      </c>
+      <c r="H6">
         <v>2.86825052501032</v>
       </c>
-      <c r="C6">
+      <c r="I6">
+        <v>28925.1268683664</v>
+      </c>
+      <c r="J6">
+        <v>33644.9282220364</v>
+      </c>
+      <c r="K6">
+        <v>2.11736543407739</v>
+      </c>
+      <c r="L6">
+        <v>30.6</v>
+      </c>
+      <c r="M6">
+        <v>1.75563025474548</v>
+      </c>
+      <c r="N6">
+        <v>23.1521854419976</v>
+      </c>
+      <c r="O6">
+        <v>45.7123683832106</v>
+      </c>
+      <c r="P6">
+        <v>42.5896362595371</v>
+      </c>
+      <c r="Q6">
+        <v>26.2116609694066</v>
+      </c>
+      <c r="R6">
         <v>2.14208964640241</v>
       </c>
-      <c r="D6">
+      <c r="S6">
         <v>5.70290624262412</v>
       </c>
-      <c r="E6">
+      <c r="T6">
+        <v>80.16341463414631</v>
+      </c>
+      <c r="U6">
+        <v>2.10435083527246</v>
+      </c>
+      <c r="V6">
+        <v>-3.38008016825818</v>
+      </c>
+      <c r="W6">
+        <v>0.345115303993225</v>
+      </c>
+      <c r="X6">
+        <v>62707588</v>
+      </c>
+      <c r="Y6">
+        <v>0.1</v>
+      </c>
+      <c r="Z6">
+        <v>1.21646451950073</v>
+      </c>
+      <c r="AA6">
+        <v>1.42519283294678</v>
+      </c>
+      <c r="AB6">
         <v>22.3223206875365</v>
       </c>
-      <c r="F6">
+      <c r="AC6">
+        <v>77353273268.9503</v>
+      </c>
+      <c r="AD6">
+        <v>1.42672975364213</v>
+      </c>
+      <c r="AE6">
+        <v>53.7497648292028</v>
+      </c>
+      <c r="AF6">
         <v>8.914</v>
       </c>
+      <c r="AG6">
+        <v>76.883</v>
+      </c>
+      <c r="AH6">
+        <v>1.45645833015442</v>
+      </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:34">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
-      <c r="B7">
+      <c r="D7">
+        <v>1.3575382232666</v>
+      </c>
+      <c r="E7">
+        <v>-0.00650919177703098</v>
+      </c>
+      <c r="F7">
+        <v>80.324329471898</v>
+      </c>
+      <c r="G7">
+        <v>28.1635565257399</v>
+      </c>
+      <c r="H7">
         <v>1.88856584109286</v>
       </c>
-      <c r="C7">
+      <c r="I7">
+        <v>30431.2367240202</v>
+      </c>
+      <c r="J7">
+        <v>34696.3718316971</v>
+      </c>
+      <c r="K7">
+        <v>1.1253537135494</v>
+      </c>
+      <c r="L7">
+        <v>29.8</v>
+      </c>
+      <c r="M7">
+        <v>1.66645479202271</v>
+      </c>
+      <c r="N7">
+        <v>23.1175353538954</v>
+      </c>
+      <c r="O7">
+        <v>45.7486480076561</v>
+      </c>
+      <c r="P7">
+        <v>42.7236277428812</v>
+      </c>
+      <c r="Q7">
+        <v>27.65927959839</v>
+      </c>
+      <c r="R7">
         <v>1.74586936380482</v>
       </c>
-      <c r="D7">
+      <c r="S7">
         <v>5.6327710879244</v>
       </c>
-      <c r="E7">
+      <c r="T7">
+        <v>80.16341463414631</v>
+      </c>
+      <c r="U7">
+        <v>2.02370691892637</v>
+      </c>
+      <c r="V7">
+        <v>-3.3039116931965</v>
+      </c>
+      <c r="W7">
+        <v>0.399723917245865</v>
+      </c>
+      <c r="X7">
+        <v>63180854</v>
+      </c>
+      <c r="Y7">
+        <v>0.1</v>
+      </c>
+      <c r="Z7">
+        <v>1.24496161937714</v>
+      </c>
+      <c r="AA7">
+        <v>1.40783047676086</v>
+      </c>
+      <c r="AB7">
         <v>22.405869035214</v>
       </c>
-      <c r="F7">
+      <c r="AC7">
+        <v>74359915676.4761</v>
+      </c>
+      <c r="AD7">
+        <v>1.22407209995772</v>
+      </c>
+      <c r="AE7">
+        <v>55.8228361241299</v>
+      </c>
+      <c r="AF7">
         <v>8.882</v>
       </c>
+      <c r="AG7">
+        <v>77.13</v>
+      </c>
+      <c r="AH7">
+        <v>1.476771235466</v>
+      </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:34">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
-      <c r="B8">
+      <c r="D8">
+        <v>1.45506083965302</v>
+      </c>
+      <c r="E8">
+        <v>0.0221896585541474</v>
+      </c>
+      <c r="F8">
+        <v>84.3572835148986</v>
+      </c>
+      <c r="G8">
+        <v>28.9278484836141</v>
+      </c>
+      <c r="H8">
         <v>2.71406448755236</v>
       </c>
-      <c r="C8">
+      <c r="I8">
+        <v>32430.4443144707</v>
+      </c>
+      <c r="J8">
+        <v>36431.5658906555</v>
+      </c>
+      <c r="K8">
+        <v>2.00131130247657</v>
+      </c>
+      <c r="L8">
+        <v>29.7</v>
+      </c>
+      <c r="M8">
+        <v>1.62847626209259</v>
+      </c>
+      <c r="N8">
+        <v>22.7854420708586</v>
+      </c>
+      <c r="O8">
+        <v>45.247946285329</v>
+      </c>
+      <c r="P8">
+        <v>42.9995642519304</v>
+      </c>
+      <c r="Q8">
+        <v>28.9414290456532</v>
+      </c>
+      <c r="R8">
         <v>1.67512449608723</v>
       </c>
-      <c r="D8">
+      <c r="S8">
         <v>5.37270744828272</v>
       </c>
-      <c r="E8">
+      <c r="T8">
+        <v>80.81219512195121</v>
+      </c>
+      <c r="U8">
+        <v>1.97509829987374</v>
+      </c>
+      <c r="V8">
+        <v>-2.43658142963503</v>
+      </c>
+      <c r="W8">
+        <v>0.595505774021149</v>
+      </c>
+      <c r="X8">
+        <v>63622342</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>1.23982167243958</v>
+      </c>
+      <c r="AA8">
+        <v>1.46217286586761</v>
+      </c>
+      <c r="AB8">
         <v>22.6603947257799</v>
       </c>
-      <c r="F8">
+      <c r="AC8">
+        <v>98239163382.50861</v>
+      </c>
+      <c r="AD8">
+        <v>1.41916447455224</v>
+      </c>
+      <c r="AE8">
+        <v>57.8692775292673</v>
+      </c>
+      <c r="AF8">
         <v>8.832000000000001</v>
       </c>
+      <c r="AG8">
+        <v>77.377</v>
+      </c>
+      <c r="AH8">
+        <v>1.29872286319733</v>
+      </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:34">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
-      <c r="B9">
+      <c r="D9">
+        <v>1.45600175857544</v>
+      </c>
+      <c r="E9">
+        <v>-0.328279950461903</v>
+      </c>
+      <c r="F9">
+        <v>88.974306564356</v>
+      </c>
+      <c r="G9">
+        <v>28.8585344688926</v>
+      </c>
+      <c r="H9">
         <v>2.53048188351066</v>
       </c>
-      <c r="C9">
+      <c r="I9">
+        <v>34067.4661475639</v>
+      </c>
+      <c r="J9">
+        <v>41486.1907828787</v>
+      </c>
+      <c r="K9">
+        <v>1.89856745333175</v>
+      </c>
+      <c r="L9">
+        <v>32.4</v>
+      </c>
+      <c r="M9">
+        <v>1.46457493305206</v>
+      </c>
+      <c r="N9">
+        <v>22.4734674757104</v>
+      </c>
+      <c r="O9">
+        <v>44.9111535137718</v>
+      </c>
+      <c r="P9">
+        <v>42.4848634559389</v>
+      </c>
+      <c r="Q9">
+        <v>29.2940266620733</v>
+      </c>
+      <c r="R9">
         <v>1.4879980595386</v>
       </c>
-      <c r="D9">
+      <c r="S9">
         <v>5.47711848457112</v>
       </c>
-      <c r="E9">
+      <c r="T9">
+        <v>81.1121951219512</v>
+      </c>
+      <c r="U9">
+        <v>1.90752863357749</v>
+      </c>
+      <c r="V9">
+        <v>-2.56265067073683</v>
+      </c>
+      <c r="W9">
+        <v>0.5630007982254031</v>
+      </c>
+      <c r="X9">
+        <v>64016890</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>1.28756642341614</v>
+      </c>
+      <c r="AA9">
+        <v>1.45637440681458</v>
+      </c>
+      <c r="AB9">
         <v>22.2192097607056</v>
       </c>
-      <c r="F9">
+      <c r="AC9">
+        <v>115487080914.377</v>
+      </c>
+      <c r="AD9">
+        <v>1.4126915622981</v>
+      </c>
+      <c r="AE9">
+        <v>58.1525611309659</v>
+      </c>
+      <c r="AF9">
         <v>8.007999999999999</v>
       </c>
+      <c r="AG9">
+        <v>77.621</v>
+      </c>
+      <c r="AH9">
+        <v>1.2597668170929</v>
+      </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:34">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
       <c r="B10">
+        <v>2.96443634829966</v>
+      </c>
+      <c r="C10">
+        <v>3.24235571721792</v>
+      </c>
+      <c r="D10">
+        <v>1.39503479003906</v>
+      </c>
+      <c r="E10">
+        <v>-0.962244945077225</v>
+      </c>
+      <c r="F10">
+        <v>92.6357426084034</v>
+      </c>
+      <c r="G10">
+        <v>29.1990596782502</v>
+      </c>
+      <c r="H10">
         <v>0.380171435849121</v>
       </c>
-      <c r="C10">
+      <c r="I10">
+        <v>35053.2627069116</v>
+      </c>
+      <c r="J10">
+        <v>45464.8181385158</v>
+      </c>
+      <c r="K10">
+        <v>-0.178410661195599</v>
+      </c>
+      <c r="L10">
+        <v>33</v>
+      </c>
+      <c r="M10">
+        <v>1.57403433322906</v>
+      </c>
+      <c r="N10">
+        <v>22.5895511441534</v>
+      </c>
+      <c r="O10">
+        <v>45.2341073217247</v>
+      </c>
+      <c r="P10">
+        <v>42.4509058971215</v>
+      </c>
+      <c r="Q10">
+        <v>29.9807331629246</v>
+      </c>
+      <c r="R10">
         <v>2.81286194914787</v>
       </c>
-      <c r="D10">
+      <c r="S10">
         <v>5.69829583364532</v>
       </c>
-      <c r="E10">
+      <c r="T10">
+        <v>81.2146341463415</v>
+      </c>
+      <c r="U10">
+        <v>1.89707589581907</v>
+      </c>
+      <c r="V10">
+        <v>-2.9929300994367</v>
+      </c>
+      <c r="W10">
+        <v>0.543759167194366</v>
+      </c>
+      <c r="X10">
+        <v>64375116</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>1.28425264358521</v>
+      </c>
+      <c r="AA10">
+        <v>1.49627375602722</v>
+      </c>
+      <c r="AB10">
         <v>22.0891842345504</v>
       </c>
-      <c r="F10">
+      <c r="AC10">
+        <v>103306201680.133</v>
+      </c>
+      <c r="AD10">
+        <v>1.13689655145287</v>
+      </c>
+      <c r="AE10">
+        <v>59.1797928411748</v>
+      </c>
+      <c r="AF10">
         <v>7.386</v>
       </c>
+      <c r="AG10">
+        <v>77.86799999999999</v>
+      </c>
+      <c r="AH10">
+        <v>1.30479431152344</v>
+      </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:34">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
       <c r="B11">
+        <v>3.65846380276455</v>
+      </c>
+      <c r="C11">
+        <v>4.58399416878334</v>
+      </c>
+      <c r="D11">
+        <v>1.4299693107605</v>
+      </c>
+      <c r="E11">
+        <v>-0.81848014778611</v>
+      </c>
+      <c r="F11">
+        <v>95.09664072478709</v>
+      </c>
+      <c r="G11">
+        <v>25.8809482311608</v>
+      </c>
+      <c r="H11">
         <v>-2.82455153714783</v>
       </c>
-      <c r="C11">
+      <c r="I11">
+        <v>34666.9598878294</v>
+      </c>
+      <c r="J11">
+        <v>41728.0884164132</v>
+      </c>
+      <c r="K11">
+        <v>-3.32212444604225</v>
+      </c>
+      <c r="L11">
+        <v>32.7</v>
+      </c>
+      <c r="M11">
+        <v>1.47705447673798</v>
+      </c>
+      <c r="N11">
+        <v>24.0880419778451</v>
+      </c>
+      <c r="O11">
+        <v>48.4059324731452</v>
+      </c>
+      <c r="P11">
+        <v>41.8198464935277</v>
+      </c>
+      <c r="Q11">
+        <v>26.3181640716005</v>
+      </c>
+      <c r="R11">
         <v>0.0876204781574486</v>
       </c>
-      <c r="D11">
+      <c r="S11">
         <v>4.87996785696563</v>
       </c>
-      <c r="E11">
+      <c r="T11">
+        <v>81.4146341463415</v>
+      </c>
+      <c r="U11">
+        <v>2.09814733452729</v>
+      </c>
+      <c r="V11">
+        <v>-7.0447240428213</v>
+      </c>
+      <c r="W11">
+        <v>0.512012898921967</v>
+      </c>
+      <c r="X11">
+        <v>64706436</v>
+      </c>
+      <c r="Y11">
+        <v>0.1</v>
+      </c>
+      <c r="Z11">
+        <v>1.21470284461975</v>
+      </c>
+      <c r="AA11">
+        <v>1.44575703144073</v>
+      </c>
+      <c r="AB11">
         <v>20.7468106096774</v>
       </c>
-      <c r="F11">
+      <c r="AC11">
+        <v>131785833333.227</v>
+      </c>
+      <c r="AD11">
+        <v>1.86200746224824</v>
+      </c>
+      <c r="AE11">
+        <v>52.1991123027613</v>
+      </c>
+      <c r="AF11">
         <v>9.122</v>
       </c>
+      <c r="AG11">
+        <v>78.117</v>
+      </c>
+      <c r="AH11">
+        <v>1.24453508853912</v>
+      </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:34">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
       <c r="B12">
+        <v>3.88993974941601</v>
+      </c>
+      <c r="C12">
+        <v>4.3272048253125</v>
+      </c>
+      <c r="D12">
+        <v>1.48775613307953</v>
+      </c>
+      <c r="E12">
+        <v>-0.832545468638349</v>
+      </c>
+      <c r="F12">
+        <v>95.8471452301569</v>
+      </c>
+      <c r="G12">
+        <v>27.8264880915553</v>
+      </c>
+      <c r="H12">
         <v>2.00032476039051</v>
       </c>
-      <c r="C12">
+      <c r="I12">
+        <v>35911.5438581409</v>
+      </c>
+      <c r="J12">
+        <v>40694.8211697025</v>
+      </c>
+      <c r="K12">
+        <v>1.49872466177408</v>
+      </c>
+      <c r="L12">
+        <v>33.7</v>
+      </c>
+      <c r="M12">
+        <v>1.46266102790833</v>
+      </c>
+      <c r="N12">
+        <v>23.9798091765185</v>
+      </c>
+      <c r="O12">
+        <v>49.6925291037396</v>
+      </c>
+      <c r="P12">
+        <v>43.2656767272935</v>
+      </c>
+      <c r="Q12">
+        <v>28.7610671562408</v>
+      </c>
+      <c r="R12">
         <v>1.53112270420927</v>
       </c>
-      <c r="D12">
+      <c r="S12">
         <v>4.94337031084377</v>
       </c>
-      <c r="E12">
+      <c r="T12">
+        <v>81.66341463414631</v>
+      </c>
+      <c r="U12">
+        <v>1.96941935275241</v>
+      </c>
+      <c r="V12">
+        <v>-7.04496539233419</v>
+      </c>
+      <c r="W12">
+        <v>0.681087553501129</v>
+      </c>
+      <c r="X12">
+        <v>65026211</v>
+      </c>
+      <c r="Y12">
+        <v>0.1</v>
+      </c>
+      <c r="Z12">
+        <v>1.31016075611115</v>
+      </c>
+      <c r="AA12">
+        <v>1.49973154067993</v>
+      </c>
+      <c r="AB12">
         <v>21.9860264776611</v>
       </c>
-      <c r="F12">
+      <c r="AC12">
+        <v>165852088071.189</v>
+      </c>
+      <c r="AD12">
+        <v>2.20263034447716</v>
+      </c>
+      <c r="AE12">
+        <v>56.587555247796</v>
+      </c>
+      <c r="AF12">
         <v>9.279</v>
       </c>
+      <c r="AG12">
+        <v>78.369</v>
+      </c>
+      <c r="AH12">
+        <v>1.20285654067993</v>
+      </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:34">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
       <c r="B13">
+        <v>3.89022009059431</v>
+      </c>
+      <c r="C13">
+        <v>4.89276263549823</v>
+      </c>
+      <c r="D13">
+        <v>1.53777325153351</v>
+      </c>
+      <c r="E13">
+        <v>-1.02802797917579</v>
+      </c>
+      <c r="F13">
+        <v>96.6491919516285</v>
+      </c>
+      <c r="G13">
+        <v>29.538847336075</v>
+      </c>
+      <c r="H13">
         <v>2.43757653729007</v>
       </c>
-      <c r="C13">
+      <c r="I13">
+        <v>37510.3759898714</v>
+      </c>
+      <c r="J13">
+        <v>43929.7840873812</v>
+      </c>
+      <c r="K13">
+        <v>1.94433505424516</v>
+      </c>
+      <c r="L13">
+        <v>33.3</v>
+      </c>
+      <c r="M13">
+        <v>1.39230680465698</v>
+      </c>
+      <c r="N13">
+        <v>23.7010905265759</v>
+      </c>
+      <c r="O13">
+        <v>47.927974289251</v>
+      </c>
+      <c r="P13">
+        <v>42.9691339303891</v>
+      </c>
+      <c r="Q13">
+        <v>31.0667881455656</v>
+      </c>
+      <c r="R13">
         <v>2.11159795174999</v>
       </c>
-      <c r="D13">
+      <c r="S13">
         <v>5.39319057986573</v>
       </c>
-      <c r="E13">
+      <c r="T13">
+        <v>82.1146341463415</v>
+      </c>
+      <c r="U13">
+        <v>1.89140621361087</v>
+      </c>
+      <c r="V13">
+        <v>-5.23260432092581</v>
+      </c>
+      <c r="W13">
+        <v>0.602992832660675</v>
+      </c>
+      <c r="X13">
+        <v>65340830</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>1.15604257583618</v>
+      </c>
+      <c r="AA13">
+        <v>1.42973482608795</v>
+      </c>
+      <c r="AB13">
         <v>21.8260251212647</v>
       </c>
-      <c r="F13">
+      <c r="AC13">
+        <v>168490291143.589</v>
+      </c>
+      <c r="AD13">
+        <v>1.94576614808198</v>
+      </c>
+      <c r="AE13">
+        <v>60.6056354816406</v>
+      </c>
+      <c r="AF13">
         <v>9.228</v>
       </c>
+      <c r="AG13">
+        <v>78.622</v>
+      </c>
+      <c r="AH13">
+        <v>1.17066836357117</v>
+      </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:34">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
       <c r="B14">
+        <v>4.26650883747211</v>
+      </c>
+      <c r="C14">
+        <v>4.29452327369679</v>
+      </c>
+      <c r="D14">
+        <v>1.4719694852829</v>
+      </c>
+      <c r="E14">
+        <v>-1.22530807843013</v>
+      </c>
+      <c r="F14">
+        <v>96.57854929593719</v>
+      </c>
+      <c r="G14">
+        <v>30.3556786527444</v>
+      </c>
+      <c r="H14">
         <v>0.183835264973013</v>
       </c>
-      <c r="C14">
+      <c r="I14">
+        <v>37671.0239268565</v>
+      </c>
+      <c r="J14">
+        <v>40863.5814412333</v>
+      </c>
+      <c r="K14">
+        <v>-0.299598729272304</v>
+      </c>
+      <c r="L14">
+        <v>33.1</v>
+      </c>
+      <c r="M14">
+        <v>1.37338125705719</v>
+      </c>
+      <c r="N14">
+        <v>23.9564328020669</v>
+      </c>
+      <c r="O14">
+        <v>48.5371716441042</v>
+      </c>
+      <c r="P14">
+        <v>43.8790803963843</v>
+      </c>
+      <c r="Q14">
+        <v>31.3032784243658</v>
+      </c>
+      <c r="R14">
         <v>1.95419531613501</v>
       </c>
-      <c r="D14">
+      <c r="S14">
         <v>5.15448325381935</v>
       </c>
-      <c r="E14">
+      <c r="T14">
+        <v>81.9682926829268</v>
+      </c>
+      <c r="U14">
+        <v>1.87108059984757</v>
+      </c>
+      <c r="V14">
+        <v>-4.94601627257407</v>
+      </c>
+      <c r="W14">
+        <v>0.554941534996033</v>
+      </c>
+      <c r="X14">
+        <v>65657659</v>
+      </c>
+      <c r="Y14">
+        <v>0.1</v>
+      </c>
+      <c r="Z14">
+        <v>1.12417411804199</v>
+      </c>
+      <c r="AA14">
+        <v>1.43693244457245</v>
+      </c>
+      <c r="AB14">
         <v>22.608974141338</v>
       </c>
-      <c r="F14">
+      <c r="AC14">
+        <v>184521825603.75</v>
+      </c>
+      <c r="AD14">
+        <v>2.24469971191405</v>
+      </c>
+      <c r="AE14">
+        <v>61.6589570771102</v>
+      </c>
+      <c r="AF14">
         <v>9.840999999999999</v>
       </c>
+      <c r="AG14">
+        <v>78.878</v>
+      </c>
+      <c r="AH14">
+        <v>1.23810577392578</v>
+      </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:34">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
       <c r="B15">
+        <v>4.53258062385818</v>
+      </c>
+      <c r="C15">
+        <v>4.49543407979547</v>
+      </c>
+      <c r="D15">
+        <v>1.30433368682861</v>
+      </c>
+      <c r="E15">
+        <v>-0.59799045690811</v>
+      </c>
+      <c r="F15">
+        <v>95.8769626871841</v>
+      </c>
+      <c r="G15">
+        <v>30.5912853427773</v>
+      </c>
+      <c r="H15">
         <v>0.781756446231</v>
       </c>
-      <c r="C15">
+      <c r="I15">
+        <v>39583.3520435045</v>
+      </c>
+      <c r="J15">
+        <v>42669.1795111893</v>
+      </c>
+      <c r="K15">
+        <v>0.26214454973659</v>
+      </c>
+      <c r="L15">
+        <v>32.5</v>
+      </c>
+      <c r="M15">
+        <v>1.48205244541168</v>
+      </c>
+      <c r="N15">
+        <v>24.0757206386355</v>
+      </c>
+      <c r="O15">
+        <v>49.0717319139337</v>
+      </c>
+      <c r="P15">
+        <v>44.7264579054071</v>
+      </c>
+      <c r="Q15">
+        <v>31.2279485306189</v>
+      </c>
+      <c r="R15">
         <v>0.863715497861873</v>
       </c>
-      <c r="D15">
+      <c r="S15">
         <v>4.52542034384841</v>
       </c>
-      <c r="E15">
+      <c r="T15">
+        <v>82.21951219512199</v>
+      </c>
+      <c r="U15">
+        <v>1.84987591828694</v>
+      </c>
+      <c r="V15">
+        <v>-4.54786773836928</v>
+      </c>
+      <c r="W15">
+        <v>0.448744118213654</v>
+      </c>
+      <c r="X15">
+        <v>65997932</v>
+      </c>
+      <c r="Y15">
+        <v>0.1</v>
+      </c>
+      <c r="Z15">
+        <v>1.14989483356476</v>
+      </c>
+      <c r="AA15">
+        <v>1.40236282348633</v>
+      </c>
+      <c r="AB15">
         <v>23.2041011683014</v>
       </c>
-      <c r="F15">
+      <c r="AC15">
+        <v>145161108178.662</v>
+      </c>
+      <c r="AD15">
+        <v>1.70354807584636</v>
+      </c>
+      <c r="AE15">
+        <v>61.8192338733962</v>
+      </c>
+      <c r="AF15">
         <v>9.913</v>
       </c>
+      <c r="AG15">
+        <v>79.13500000000001</v>
+      </c>
+      <c r="AH15">
+        <v>1.21920275688171</v>
+      </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:34">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
       <c r="B16">
+        <v>4.2366463637383</v>
+      </c>
+      <c r="C16">
+        <v>3.72567893768622</v>
+      </c>
+      <c r="D16">
+        <v>1.2879855632782</v>
+      </c>
+      <c r="E16">
+        <v>-0.9627336993811511</v>
+      </c>
+      <c r="F16">
+        <v>93.9159081503646</v>
+      </c>
+      <c r="G16">
+        <v>30.741812901515</v>
+      </c>
+      <c r="H16">
         <v>0.997832947295251</v>
       </c>
-      <c r="C16">
+      <c r="I16">
+        <v>40218.1258637776</v>
+      </c>
+      <c r="J16">
+        <v>43148.0459288416</v>
+      </c>
+      <c r="K16">
+        <v>0.519383764691739</v>
+      </c>
+      <c r="L16">
+        <v>32.3</v>
+      </c>
+      <c r="M16">
+        <v>1.41287088394165</v>
+      </c>
+      <c r="N16">
+        <v>24.081442589149</v>
+      </c>
+      <c r="O16">
+        <v>49.1207847434763</v>
+      </c>
+      <c r="P16">
+        <v>44.9324802595085</v>
+      </c>
+      <c r="Q16">
+        <v>31.4574540364356</v>
+      </c>
+      <c r="R16">
         <v>0.507758822937963</v>
       </c>
-      <c r="D16">
+      <c r="S16">
         <v>4.31671983020436</v>
       </c>
-      <c r="E16">
+      <c r="T16">
+        <v>82.71951219512199</v>
+      </c>
+      <c r="U16">
+        <v>1.86296143947269</v>
+      </c>
+      <c r="V16">
+        <v>-4.30981907646774</v>
+      </c>
+      <c r="W16">
+        <v>0.300568491220474</v>
+      </c>
+      <c r="X16">
+        <v>66312067</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>1.07406842708588</v>
+      </c>
+      <c r="AA16">
+        <v>1.45350301265717</v>
+      </c>
+      <c r="AB16">
         <v>23.1556593525911</v>
       </c>
-      <c r="F16">
+      <c r="AC16">
+        <v>143977104333.434</v>
+      </c>
+      <c r="AD16">
+        <v>1.64889771434924</v>
+      </c>
+      <c r="AE16">
+        <v>62.1992669379507</v>
+      </c>
+      <c r="AF16">
         <v>10.273</v>
       </c>
+      <c r="AG16">
+        <v>79.39400000000001</v>
+      </c>
+      <c r="AH16">
+        <v>1.21813237667084</v>
+      </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:34">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
       <c r="B17">
+        <v>4.67838137015214</v>
+      </c>
+      <c r="C17">
+        <v>3.52308121172511</v>
+      </c>
+      <c r="D17">
+        <v>1.24783480167389</v>
+      </c>
+      <c r="E17">
+        <v>-0.334528437032909</v>
+      </c>
+      <c r="F17">
+        <v>94.9454202268228</v>
+      </c>
+      <c r="G17">
+        <v>31.6934947262689</v>
+      </c>
+      <c r="H17">
         <v>1.06675474783462</v>
       </c>
-      <c r="C17">
+      <c r="I17">
+        <v>40916.10535718</v>
+      </c>
+      <c r="J17">
+        <v>36702.4323733379</v>
+      </c>
+      <c r="K17">
+        <v>0.708030590350688</v>
+      </c>
+      <c r="L17">
+        <v>32.7</v>
+      </c>
+      <c r="M17">
+        <v>1.41732227802277</v>
+      </c>
+      <c r="N17">
+        <v>23.7757617692292</v>
+      </c>
+      <c r="O17">
+        <v>48.4491880082217</v>
+      </c>
+      <c r="P17">
+        <v>44.6530065209365</v>
+      </c>
+      <c r="Q17">
+        <v>31.8111924693795</v>
+      </c>
+      <c r="R17">
         <v>0.0375143805125298</v>
       </c>
-      <c r="D17">
+      <c r="S17">
         <v>4.05880131397992</v>
       </c>
-      <c r="E17">
+      <c r="T17">
+        <v>82.3219512195122</v>
+      </c>
+      <c r="U17">
+        <v>1.87225828127684</v>
+      </c>
+      <c r="V17">
+        <v>-3.87230571650352</v>
+      </c>
+      <c r="W17">
+        <v>0.0977598056197166</v>
+      </c>
+      <c r="X17">
+        <v>66548272</v>
+      </c>
+      <c r="Y17">
+        <v>0.1</v>
+      </c>
+      <c r="Z17">
+        <v>1.11580765247345</v>
+      </c>
+      <c r="AA17">
+        <v>1.36679553985596</v>
+      </c>
+      <c r="AB17">
         <v>23.2974119760792</v>
       </c>
-      <c r="F17">
+      <c r="AC17">
+        <v>138198984338.294</v>
+      </c>
+      <c r="AD17">
+        <v>1.82304349468037</v>
+      </c>
+      <c r="AE17">
+        <v>63.5046871956484</v>
+      </c>
+      <c r="AF17">
         <v>10.354</v>
       </c>
+      <c r="AG17">
+        <v>79.655</v>
+      </c>
+      <c r="AH17">
+        <v>1.20674192905426</v>
+      </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:34">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
       <c r="B18">
+        <v>5.15137252858059</v>
+      </c>
+      <c r="C18">
+        <v>3.49852745916487</v>
+      </c>
+      <c r="D18">
+        <v>1.32828891277313</v>
+      </c>
+      <c r="E18">
+        <v>-0.538632351885894</v>
+      </c>
+      <c r="F18">
+        <v>97.4904687619857</v>
+      </c>
+      <c r="G18">
+        <v>31.498210070063</v>
+      </c>
+      <c r="H18">
         <v>0.860031075424033</v>
       </c>
-      <c r="C18">
+      <c r="I18">
+        <v>42880.2351355431</v>
+      </c>
+      <c r="J18">
+        <v>37024.2157133669</v>
+      </c>
+      <c r="K18">
+        <v>0.594243752389232</v>
+      </c>
+      <c r="L18">
+        <v>31.9</v>
+      </c>
+      <c r="M18">
+        <v>1.38062357902527</v>
+      </c>
+      <c r="N18">
+        <v>23.7569423186251</v>
+      </c>
+      <c r="O18">
+        <v>48.1500427991658</v>
+      </c>
+      <c r="P18">
+        <v>44.4509842015877</v>
+      </c>
+      <c r="Q18">
+        <v>31.8445463682721</v>
+      </c>
+      <c r="R18">
         <v>0.183334861123829</v>
       </c>
-      <c r="D18">
+      <c r="S18">
         <v>3.84057871889639</v>
       </c>
-      <c r="E18">
+      <c r="T18">
+        <v>82.57317073170729</v>
+      </c>
+      <c r="U18">
+        <v>1.91728236804142</v>
+      </c>
+      <c r="V18">
+        <v>-3.86604793076428</v>
+      </c>
+      <c r="W18">
+        <v>-0.106349594891071</v>
+      </c>
+      <c r="X18">
+        <v>66724104</v>
+      </c>
+      <c r="Y18">
+        <v>0.1</v>
+      </c>
+      <c r="Z18">
+        <v>1.05861842632294</v>
+      </c>
+      <c r="AA18">
+        <v>1.35156190395355</v>
+      </c>
+      <c r="AB18">
         <v>23.1463283405753</v>
       </c>
-      <c r="F18">
+      <c r="AC18">
+        <v>145866068770.183</v>
+      </c>
+      <c r="AD18">
+        <v>1.92813809141289</v>
+      </c>
+      <c r="AE18">
+        <v>63.3427564383351</v>
+      </c>
+      <c r="AF18">
         <v>10.057</v>
       </c>
+      <c r="AG18">
+        <v>79.917</v>
+      </c>
+      <c r="AH18">
+        <v>1.13691318035126</v>
+      </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:34">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
       <c r="B19">
+        <v>5.37401395271466</v>
+      </c>
+      <c r="C19">
+        <v>2.85084082112563</v>
+      </c>
+      <c r="D19">
+        <v>1.22452700138092</v>
+      </c>
+      <c r="E19">
+        <v>-0.474615185215669</v>
+      </c>
+      <c r="F19">
+        <v>101.617830234188</v>
+      </c>
+      <c r="G19">
+        <v>32.311834044929</v>
+      </c>
+      <c r="H19">
         <v>2.08361485997399</v>
       </c>
-      <c r="C19">
+      <c r="I19">
+        <v>44469.1458856805</v>
+      </c>
+      <c r="J19">
+        <v>38687.1626407164</v>
+      </c>
+      <c r="K19">
+        <v>1.78779549384231</v>
+      </c>
+      <c r="L19">
+        <v>31.6</v>
+      </c>
+      <c r="M19">
+        <v>1.30890679359436</v>
+      </c>
+      <c r="N19">
+        <v>23.7013842025535</v>
+      </c>
+      <c r="O19">
+        <v>48.466341621356</v>
+      </c>
+      <c r="P19">
+        <v>45.0848754876607</v>
+      </c>
+      <c r="Q19">
+        <v>33.0840141110421</v>
+      </c>
+      <c r="R19">
         <v>1.03228275064667</v>
       </c>
-      <c r="D19">
+      <c r="S19">
         <v>3.58615521092809</v>
       </c>
-      <c r="E19">
+      <c r="T19">
+        <v>82.57560975609761</v>
+      </c>
+      <c r="U19">
+        <v>1.90864201234437</v>
+      </c>
+      <c r="V19">
+        <v>-3.42402442225258</v>
+      </c>
+      <c r="W19">
+        <v>0.265701532363892</v>
+      </c>
+      <c r="X19">
+        <v>66918020</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>1.14648473262787</v>
+      </c>
+      <c r="AA19">
+        <v>1.39806187152863</v>
+      </c>
+      <c r="AB19">
         <v>23.7863349624871</v>
       </c>
-      <c r="F19">
+      <c r="AC19">
+        <v>156322431109.247</v>
+      </c>
+      <c r="AD19">
+        <v>1.90966013668591</v>
+      </c>
+      <c r="AE19">
+        <v>65.39584815597109</v>
+      </c>
+      <c r="AF19">
         <v>9.409000000000001</v>
       </c>
+      <c r="AG19">
+        <v>80.18000000000001</v>
+      </c>
+      <c r="AH19">
+        <v>1.15271818637848</v>
+      </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:34">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
       <c r="B20">
+        <v>5.41296527913485</v>
+      </c>
+      <c r="C20">
+        <v>2.74917800998469</v>
+      </c>
+      <c r="D20">
+        <v>1.28155159950256</v>
+      </c>
+      <c r="E20">
+        <v>-0.735670615255371</v>
+      </c>
+      <c r="F20">
+        <v>104.624051971951</v>
+      </c>
+      <c r="G20">
+        <v>32.9179818922164</v>
+      </c>
+      <c r="H20">
         <v>1.64590872395887</v>
       </c>
-      <c r="C20">
+      <c r="I20">
+        <v>46381.0590629457</v>
+      </c>
+      <c r="J20">
+        <v>41418.1766484844</v>
+      </c>
+      <c r="K20">
+        <v>1.28216603702126</v>
+      </c>
+      <c r="L20">
+        <v>32.4</v>
+      </c>
+      <c r="M20">
+        <v>1.41971850395203</v>
+      </c>
+      <c r="N20">
+        <v>23.3500758354509</v>
+      </c>
+      <c r="O20">
+        <v>47.1000773214216</v>
+      </c>
+      <c r="P20">
+        <v>44.7259377621146</v>
+      </c>
+      <c r="Q20">
+        <v>33.8842788890102</v>
+      </c>
+      <c r="R20">
         <v>1.85081508315501</v>
       </c>
-      <c r="D20">
+      <c r="S20">
         <v>3.64113141989423</v>
       </c>
-      <c r="E20">
+      <c r="T20">
+        <v>82.6756097560976</v>
+      </c>
+      <c r="U20">
+        <v>1.84300872300244</v>
+      </c>
+      <c r="V20">
+        <v>-2.39420440876454</v>
+      </c>
+      <c r="W20">
+        <v>0.013894104398787</v>
+      </c>
+      <c r="X20">
+        <v>67158348</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>1.1474986076355</v>
+      </c>
+      <c r="AA20">
+        <v>1.39622473716736</v>
+      </c>
+      <c r="AB20">
         <v>24.3098642807809</v>
       </c>
-      <c r="F20">
+      <c r="AC20">
+        <v>166483400196.79</v>
+      </c>
+      <c r="AD20">
+        <v>1.83376419046355</v>
+      </c>
+      <c r="AE20">
+        <v>66.80226078122659</v>
+      </c>
+      <c r="AF20">
         <v>9.018000000000001</v>
       </c>
+      <c r="AG20">
+        <v>80.444</v>
+      </c>
+      <c r="AH20">
+        <v>1.1575254201889</v>
+      </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:34">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
       <c r="B21">
+        <v>5.52208226708401</v>
+      </c>
+      <c r="C21">
+        <v>2.51442386618475</v>
+      </c>
+      <c r="D21">
+        <v>1.24806225299835</v>
+      </c>
+      <c r="E21">
+        <v>0.587362764575748</v>
+      </c>
+      <c r="F21">
+        <v>106.913030586051</v>
+      </c>
+      <c r="G21">
+        <v>32.8895593910847</v>
+      </c>
+      <c r="H21">
         <v>2.02744646419237</v>
       </c>
-      <c r="C21">
+      <c r="I21">
+        <v>51130.4723140578</v>
+      </c>
+      <c r="J21">
+        <v>40408.2848574751</v>
+      </c>
+      <c r="K21">
+        <v>1.68870844116209</v>
+      </c>
+      <c r="L21">
+        <v>31.2</v>
+      </c>
+      <c r="M21">
+        <v>1.33822000026703</v>
+      </c>
+      <c r="N21">
+        <v>23.0348422675243</v>
+      </c>
+      <c r="O21">
+        <v>45.8897902925031</v>
+      </c>
+      <c r="P21">
+        <v>43.6550132168038</v>
+      </c>
+      <c r="Q21">
+        <v>33.5394177830602</v>
+      </c>
+      <c r="R21">
         <v>1.10825492288292</v>
       </c>
-      <c r="D21">
+      <c r="S21">
         <v>3.16512004914103</v>
       </c>
-      <c r="E21">
+      <c r="T21">
+        <v>82.8268292682927</v>
+      </c>
+      <c r="U21">
+        <v>1.8364614707329</v>
+      </c>
+      <c r="V21">
+        <v>-2.28934891556096</v>
+      </c>
+      <c r="W21">
+        <v>0.271341234445572</v>
+      </c>
+      <c r="X21">
+        <v>67382061</v>
+      </c>
+      <c r="Y21">
+        <v>0.1</v>
+      </c>
+      <c r="Z21">
+        <v>1.43153774738312</v>
+      </c>
+      <c r="AA21">
+        <v>1.37148487567902</v>
+      </c>
+      <c r="AB21">
         <v>24.6605263993177</v>
       </c>
-      <c r="F21">
+      <c r="AC21">
+        <v>189006435295.488</v>
+      </c>
+      <c r="AD21">
+        <v>2.15547480521791</v>
+      </c>
+      <c r="AE21">
+        <v>66.4289771741449</v>
+      </c>
+      <c r="AF21">
         <v>8.414999999999999</v>
       </c>
+      <c r="AG21">
+        <v>80.709</v>
+      </c>
+      <c r="AH21">
+        <v>1.11500012874603</v>
+      </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:34">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
       <c r="B22">
+        <v>5.85566091396961</v>
+      </c>
+      <c r="C22">
+        <v>2.38440087259746</v>
+      </c>
+      <c r="D22">
+        <v>1.12261998653412</v>
+      </c>
+      <c r="E22">
+        <v>-2.00313613657686</v>
+      </c>
+      <c r="F22">
+        <v>125.397439701102</v>
+      </c>
+      <c r="G22">
+        <v>28.5572228192655</v>
+      </c>
+      <c r="H22">
         <v>-7.44064589948231</v>
       </c>
-      <c r="C22">
+      <c r="I22">
+        <v>49481.8044309655</v>
+      </c>
+      <c r="J22">
+        <v>39169.8606000707</v>
+      </c>
+      <c r="K22">
+        <v>-7.74056751254994</v>
+      </c>
+      <c r="L22">
+        <v>30.7</v>
+      </c>
+      <c r="M22">
+        <v>1.2042510509491</v>
+      </c>
+      <c r="N22">
+        <v>24.8398357365701</v>
+      </c>
+      <c r="O22">
+        <v>51.9636314257982</v>
+      </c>
+      <c r="P22">
+        <v>43.3219907101665</v>
+      </c>
+      <c r="Q22">
+        <v>30.2816679047993</v>
+      </c>
+      <c r="R22">
         <v>0.476498852725014</v>
       </c>
-      <c r="D22">
+      <c r="S22">
         <v>2.36365349407572</v>
       </c>
-      <c r="E22">
+      <c r="T22">
+        <v>82.1756097560976</v>
+      </c>
+      <c r="U22">
+        <v>1.99647774299432</v>
+      </c>
+      <c r="V22">
+        <v>-8.76625917136189</v>
+      </c>
+      <c r="W22">
+        <v>0.280992835760117</v>
+      </c>
+      <c r="X22">
+        <v>67601110</v>
+      </c>
+      <c r="Y22">
+        <v>0.1</v>
+      </c>
+      <c r="Z22">
+        <v>1.18946194648743</v>
+      </c>
+      <c r="AA22">
+        <v>1.29872727394104</v>
+      </c>
+      <c r="AB22">
         <v>24.7888064416138</v>
       </c>
-      <c r="F22">
+      <c r="AC22">
+        <v>224236417867.711</v>
+      </c>
+      <c r="AD22">
+        <v>2.93207471945523</v>
+      </c>
+      <c r="AE22">
+        <v>58.8388907240647</v>
+      </c>
+      <c r="AF22">
         <v>8.009</v>
       </c>
+      <c r="AG22">
+        <v>80.97499999999999</v>
+      </c>
+      <c r="AH22">
+        <v>1.06575298309326</v>
+      </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:34">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
       <c r="B23">
+        <v>5.72243967873599</v>
+      </c>
+      <c r="C23">
+        <v>2.1692050101449</v>
+      </c>
+      <c r="D23">
+        <v>1.28193628787994</v>
+      </c>
+      <c r="E23">
+        <v>0.244238511780542</v>
+      </c>
+      <c r="F23">
+        <v>120.721909947613</v>
+      </c>
+      <c r="G23">
+        <v>31.2880499332105</v>
+      </c>
+      <c r="H23">
         <v>6.88233783360239</v>
       </c>
-      <c r="C23">
+      <c r="I23">
+        <v>52517.3354905855</v>
+      </c>
+      <c r="J23">
+        <v>43725.0999521245</v>
+      </c>
+      <c r="K23">
+        <v>6.50155219757207</v>
+      </c>
+      <c r="L23">
+        <v>31.5</v>
+      </c>
+      <c r="M23">
+        <v>1.22854030132294</v>
+      </c>
+      <c r="N23">
+        <v>24.3515984176563</v>
+      </c>
+      <c r="O23">
+        <v>49.9944440065304</v>
+      </c>
+      <c r="P23">
+        <v>43.504848267154</v>
+      </c>
+      <c r="Q23">
+        <v>32.5004326976615</v>
+      </c>
+      <c r="R23">
         <v>1.64233141038393</v>
       </c>
-      <c r="D23">
+      <c r="S23">
         <v>2.6773015454516</v>
       </c>
-      <c r="E23">
+      <c r="T23">
+        <v>82.3243902439024</v>
+      </c>
+      <c r="U23">
+        <v>1.91440611513925</v>
+      </c>
+      <c r="V23">
+        <v>-6.54907895902013</v>
+      </c>
+      <c r="W23">
+        <v>0.325612366199493</v>
+      </c>
+      <c r="X23">
+        <v>67842811</v>
+      </c>
+      <c r="Y23">
+        <v>0.1</v>
+      </c>
+      <c r="Z23">
+        <v>1.23037326335907</v>
+      </c>
+      <c r="AA23">
+        <v>1.25916755199432</v>
+      </c>
+      <c r="AB23">
         <v>23.9794445386059</v>
       </c>
-      <c r="F23">
+      <c r="AC23">
+        <v>244280333397.895</v>
+      </c>
+      <c r="AD23">
+        <v>2.65318657576471</v>
+      </c>
+      <c r="AE23">
+        <v>63.788482630872</v>
+      </c>
+      <c r="AF23">
         <v>7.874</v>
       </c>
+      <c r="AG23">
+        <v>81.242</v>
+      </c>
+      <c r="AH23">
+        <v>1.10422718524933</v>
+      </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:34">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
       <c r="B24">
+        <v>5.3461127232552</v>
+      </c>
+      <c r="C24">
+        <v>2.0781054407903</v>
+      </c>
+      <c r="D24">
+        <v>1.25943613052368</v>
+      </c>
+      <c r="E24">
+        <v>-1.43157299945545</v>
+      </c>
+      <c r="F24">
+        <v>119.225776567681</v>
+      </c>
+      <c r="G24">
+        <v>36.5036688904078</v>
+      </c>
+      <c r="H24">
         <v>2.57084047567793</v>
       </c>
-      <c r="C24">
+      <c r="I24">
+        <v>56181.0058137403</v>
+      </c>
+      <c r="J24">
+        <v>41082.8119320747</v>
+      </c>
+      <c r="K24">
+        <v>2.23598928910201</v>
+      </c>
+      <c r="L24">
+        <v>31.2</v>
+      </c>
+      <c r="M24">
+        <v>1.16521215438843</v>
+      </c>
+      <c r="N24">
+        <v>23.8613635807316</v>
+      </c>
+      <c r="O24">
+        <v>48.8338671441779</v>
+      </c>
+      <c r="P24">
+        <v>44.2550165980338</v>
+      </c>
+      <c r="Q24">
+        <v>39.2864747207143</v>
+      </c>
+      <c r="R24">
         <v>5.22236748369736</v>
       </c>
-      <c r="D24">
+      <c r="S24">
         <v>3.76186156238404</v>
       </c>
-      <c r="E24">
+      <c r="T24">
+        <v>82.12926829268289</v>
+      </c>
+      <c r="U24">
+        <v>1.93242353809568</v>
+      </c>
+      <c r="V24">
+        <v>-4.69686134286849</v>
+      </c>
+      <c r="W24">
+        <v>0.393339216709137</v>
+      </c>
+      <c r="X24">
+        <v>68065015</v>
+      </c>
+      <c r="Y24">
+        <v>0.1</v>
+      </c>
+      <c r="Z24">
+        <v>1.1889523267746</v>
+      </c>
+      <c r="AA24">
+        <v>1.18058335781097</v>
+      </c>
+      <c r="AB24">
         <v>24.534247684466</v>
       </c>
-      <c r="F24">
+      <c r="AC24">
+        <v>242415618842.022</v>
+      </c>
+      <c r="AD24">
+        <v>2.27470946365429</v>
+      </c>
+      <c r="AE24">
+        <v>75.7901436111221</v>
+      </c>
+      <c r="AF24">
         <v>7.308</v>
       </c>
+      <c r="AG24">
+        <v>81.509</v>
+      </c>
+      <c r="AH24">
+        <v>1.11015677452087</v>
+      </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:34">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
       <c r="B25">
+        <v>5.46519281476646</v>
+      </c>
+      <c r="C25">
+        <v>2.06122418440949</v>
+      </c>
+      <c r="D25">
+        <v>1.18482184410095</v>
+      </c>
+      <c r="E25">
+        <v>-1.04452732139601</v>
+      </c>
+      <c r="F25">
+        <v>112.730351800876</v>
+      </c>
+      <c r="G25">
+        <v>34.2800305804742</v>
+      </c>
+      <c r="H25">
         <v>0.936487518850853</v>
       </c>
-      <c r="C25">
+      <c r="I25">
+        <v>58317.828030698</v>
+      </c>
+      <c r="J25">
+        <v>44690.9345395117</v>
+      </c>
+      <c r="K25">
+        <v>0.607649202523703</v>
+      </c>
+      <c r="L25">
+        <v>31.8</v>
+      </c>
+      <c r="M25">
+        <v>1.14462625980377</v>
+      </c>
+      <c r="N25">
+        <v>23.1235606057224</v>
+      </c>
+      <c r="O25">
+        <v>47.3264654106394</v>
+      </c>
+      <c r="P25">
+        <v>42.2749864603668</v>
+      </c>
+      <c r="Q25">
+        <v>36.279524212719</v>
+      </c>
+      <c r="R25">
         <v>4.87835726508438</v>
       </c>
-      <c r="D25">
+      <c r="S25">
         <v>3.37281623755023</v>
       </c>
-      <c r="E25">
+      <c r="T25">
+        <v>82.92926829268291</v>
+      </c>
+      <c r="U25">
+        <v>2.05638673841337</v>
+      </c>
+      <c r="V25">
+        <v>-5.13437488064467</v>
+      </c>
+      <c r="W25">
+        <v>0.343697965145111</v>
+      </c>
+      <c r="X25">
+        <v>68287487</v>
+      </c>
+      <c r="Y25">
+        <v>0.1</v>
+      </c>
+      <c r="Z25">
+        <v>1.15350544452667</v>
+      </c>
+      <c r="AA25">
+        <v>1.18057084083557</v>
+      </c>
+      <c r="AB25">
         <v>23.1103805885841</v>
       </c>
-      <c r="F25">
+      <c r="AC25">
+        <v>240792007784.254</v>
+      </c>
+      <c r="AD25">
+        <v>2.05933939987688</v>
+      </c>
+      <c r="AE25">
+        <v>70.5595547931931</v>
+      </c>
+      <c r="AF25">
         <v>7.335</v>
       </c>
+      <c r="AG25">
+        <v>81.777</v>
+      </c>
+      <c r="AH25">
+        <v>1.15460133552551</v>
+      </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:34">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
-      <c r="B26">
+      <c r="E26">
+        <v>0.08508393256912559</v>
+      </c>
+      <c r="F26">
+        <v>107.526984042441</v>
+      </c>
+      <c r="G26">
+        <v>33.2440842472123</v>
+      </c>
+      <c r="H26">
         <v>1.16613851497229</v>
       </c>
-      <c r="C26">
+      <c r="I26">
+        <v>61321.691319446</v>
+      </c>
+      <c r="J26">
+        <v>46150.4876861593</v>
+      </c>
+      <c r="K26">
+        <v>0.827702874030308</v>
+      </c>
+      <c r="Q26">
+        <v>33.9788865095979</v>
+      </c>
+      <c r="R26">
         <v>1.99904942291464</v>
       </c>
-      <c r="F26">
+      <c r="X26">
+        <v>68516699</v>
+      </c>
+      <c r="AC26">
+        <v>282857002813.825</v>
+      </c>
+      <c r="AD26">
+        <v>2.38967602333511</v>
+      </c>
+      <c r="AE26">
+        <v>67.2229707568101</v>
+      </c>
+      <c r="AF26">
         <v>7.37</v>
+      </c>
+      <c r="AG26">
+        <v>82.044</v>
       </c>
     </row>
   </sheetData>

--- a/FRA_WB_timeseries.xlsx
+++ b/FRA_WB_timeseries.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beldjenna/Desktop/Rating Algo/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3494A9DD-64BE-6E4C-80C9-687C02DF467E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -73,8 +67,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,18 +85,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -132,33 +120,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -196,7 +175,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -230,7 +209,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -265,10 +243,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -441,11 +418,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -495,21 +472,21 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
       <c r="B2">
-        <v>1.3217235803604099</v>
+        <v>1.32172358036041</v>
       </c>
       <c r="C2">
-        <v>1.1848394944316001</v>
+        <v>1.1848394944316</v>
       </c>
       <c r="D2">
-        <v>29.758048989312901</v>
+        <v>29.7580489893129</v>
       </c>
       <c r="E2">
-        <v>4.1409999640291497</v>
+        <v>4.14099996402915</v>
       </c>
       <c r="F2">
         <v>22340.5939516217</v>
@@ -518,115 +495,113 @@
         <v>44.7395900950739</v>
       </c>
       <c r="H2">
-        <v>43.439130304069003</v>
+        <v>43.439130304069</v>
       </c>
       <c r="I2">
-        <v>28.027998042506901</v>
+        <v>28.0279980425069</v>
       </c>
       <c r="J2">
         <v>1.67595988720928</v>
       </c>
       <c r="K2">
-        <v>6.1864804255045502</v>
+        <v>6.18648042550455</v>
       </c>
       <c r="L2">
-        <v>-1.3849515034536799</v>
+        <v>-1.38495150345368</v>
       </c>
       <c r="M2">
-        <v>0.78508907556533802</v>
+        <v>0.785089075565338</v>
       </c>
       <c r="N2">
         <v>23.5306025928572</v>
       </c>
       <c r="O2">
-        <v>57.786047031819699</v>
+        <v>57.7860470318197</v>
       </c>
       <c r="P2">
         <v>59.7</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
-      <c r="B3" s="2"/>
       <c r="C3">
-        <v>1.5298994522382099</v>
+        <v>1.52989945223821</v>
       </c>
       <c r="D3">
         <v>29.4306035099419</v>
       </c>
       <c r="E3">
-        <v>1.8994670118663599</v>
+        <v>1.89946701186636</v>
       </c>
       <c r="F3">
-        <v>22331.794834303601</v>
+        <v>22331.7948343036</v>
       </c>
       <c r="G3">
-        <v>45.125961156440503</v>
+        <v>45.1259611564405</v>
       </c>
       <c r="H3">
-        <v>43.806126892551198</v>
+        <v>43.8061268925512</v>
       </c>
       <c r="I3">
-        <v>27.462629346130299</v>
+        <v>27.4626293461303</v>
       </c>
       <c r="J3">
-        <v>1.6347807954960201</v>
+        <v>1.63478079549602</v>
       </c>
       <c r="K3">
-        <v>6.1352068304687704</v>
+        <v>6.13520683046877</v>
       </c>
       <c r="L3">
         <v>-1.46983384887589</v>
       </c>
-      <c r="M3" s="2"/>
       <c r="N3">
         <v>23.563254487096</v>
       </c>
       <c r="O3">
-        <v>56.893232856072203</v>
+        <v>56.8932328560722</v>
       </c>
       <c r="P3">
         <v>59.3</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
       <c r="B4">
-        <v>1.1915851831436199</v>
+        <v>1.19158518314362</v>
       </c>
       <c r="C4">
         <v>1.18270439802011</v>
       </c>
       <c r="D4">
-        <v>28.730701759276801</v>
+        <v>28.7307017592768</v>
       </c>
       <c r="E4">
-        <v>1.0677502706941899</v>
+        <v>1.06775027069419</v>
       </c>
       <c r="F4">
         <v>24144.5727019529</v>
       </c>
       <c r="G4">
-        <v>46.148132228841298</v>
+        <v>46.1481322288413</v>
       </c>
       <c r="H4">
-        <v>43.143824638998296</v>
+        <v>43.1438246389983</v>
       </c>
       <c r="I4">
         <v>26.4018230910334</v>
       </c>
       <c r="J4">
-        <v>1.9234122872706001</v>
+        <v>1.9234122872706</v>
       </c>
       <c r="K4">
         <v>6.03730246989854</v>
       </c>
       <c r="L4">
-        <v>-3.2594062688015102</v>
+        <v>-3.25940626880151</v>
       </c>
       <c r="M4">
         <v>0.924183249473572</v>
@@ -635,63 +610,63 @@
         <v>22.764124672502</v>
       </c>
       <c r="O4">
-        <v>55.132524850310197</v>
+        <v>55.1325248503102</v>
       </c>
       <c r="P4">
         <v>61.3</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
       <c r="B5">
-        <v>1.3057560920715301</v>
+        <v>1.30575609207153</v>
       </c>
       <c r="C5">
-        <v>0.87106340687280803</v>
+        <v>0.871063406872808</v>
       </c>
       <c r="D5">
-        <v>27.136967667394401</v>
+        <v>27.1369676673944</v>
       </c>
       <c r="E5">
-        <v>0.96782718255835198</v>
+        <v>0.967827182558352</v>
       </c>
       <c r="F5">
-        <v>29479.522210117499</v>
+        <v>29479.5222101175</v>
       </c>
       <c r="G5">
-        <v>46.378152228102998</v>
+        <v>46.378152228103</v>
       </c>
       <c r="H5">
         <v>42.548360587428</v>
       </c>
       <c r="I5">
-        <v>25.461914619671401</v>
+        <v>25.4619146196714</v>
       </c>
       <c r="J5">
-        <v>2.0984721914692299</v>
+        <v>2.09847219146923</v>
       </c>
       <c r="K5">
-        <v>5.7409588825711699</v>
+        <v>5.74095888257117</v>
       </c>
       <c r="L5">
-        <v>-4.1009045851083696</v>
+        <v>-4.10090458510837</v>
       </c>
       <c r="M5">
-        <v>0.17955106496810899</v>
+        <v>0.179551064968109</v>
       </c>
       <c r="N5">
-        <v>22.293530569443799</v>
+        <v>22.2935305694438</v>
       </c>
       <c r="O5">
-        <v>52.598882287065699</v>
+        <v>52.5988822870657</v>
       </c>
       <c r="P5">
-        <v>65.400000000000006</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
@@ -699,49 +674,49 @@
         <v>1.31116378307343</v>
       </c>
       <c r="C6">
-        <v>0.43447012043998301</v>
+        <v>0.434470120439983</v>
       </c>
       <c r="D6">
-        <v>27.538103859796198</v>
+        <v>27.5381038597962</v>
       </c>
       <c r="E6">
-        <v>2.8682505250103199</v>
+        <v>2.86825052501032</v>
       </c>
       <c r="F6">
-        <v>33644.928222036397</v>
+        <v>33644.9282220364</v>
       </c>
       <c r="G6">
-        <v>45.712368383210602</v>
+        <v>45.7123683832106</v>
       </c>
       <c r="H6">
-        <v>42.589636259537102</v>
+        <v>42.5896362595371</v>
       </c>
       <c r="I6">
-        <v>26.211660969406601</v>
+        <v>26.2116609694066</v>
       </c>
       <c r="J6">
-        <v>2.1420896464024102</v>
+        <v>2.14208964640241</v>
       </c>
       <c r="K6">
-        <v>5.7029062426241204</v>
+        <v>5.70290624262412</v>
       </c>
       <c r="L6">
-        <v>-3.3800801682581798</v>
+        <v>-3.38008016825818</v>
       </c>
       <c r="M6">
-        <v>0.34511530399322499</v>
+        <v>0.345115303993225</v>
       </c>
       <c r="N6">
         <v>22.3223206875365</v>
       </c>
       <c r="O6">
-        <v>53.749764829202803</v>
+        <v>53.7497648292028</v>
       </c>
       <c r="P6">
-        <v>66.900000000000006</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+        <v>66.90000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
@@ -749,37 +724,37 @@
         <v>1.3575382232666</v>
       </c>
       <c r="C7">
-        <v>-6.5091917770309796E-3</v>
+        <v>-0.00650919177703098</v>
       </c>
       <c r="D7">
-        <v>28.163556525739899</v>
+        <v>28.1635565257399</v>
       </c>
       <c r="E7">
-        <v>1.8885658410928601</v>
+        <v>1.88856584109286</v>
       </c>
       <c r="F7">
-        <v>34696.371831697099</v>
+        <v>34696.3718316971</v>
       </c>
       <c r="G7">
-        <v>45.748648007656101</v>
+        <v>45.7486480076561</v>
       </c>
       <c r="H7">
-        <v>42.723627742881199</v>
+        <v>42.7236277428812</v>
       </c>
       <c r="I7">
         <v>27.65927959839</v>
       </c>
       <c r="J7">
-        <v>1.7458693638048199</v>
+        <v>1.74586936380482</v>
       </c>
       <c r="K7">
-        <v>5.6327710879244002</v>
+        <v>5.6327710879244</v>
       </c>
       <c r="L7">
         <v>-3.3039116931965</v>
       </c>
       <c r="M7">
-        <v>0.39972391724586498</v>
+        <v>0.399723917245865</v>
       </c>
       <c r="N7">
         <v>22.405869035214</v>
@@ -791,7 +766,7 @@
         <v>68.2</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
@@ -799,54 +774,54 @@
         <v>1.45506083965302</v>
       </c>
       <c r="C8">
-        <v>2.2189658554147399E-2</v>
+        <v>0.0221896585541474</v>
       </c>
       <c r="D8">
-        <v>28.927848483614099</v>
+        <v>28.9278484836141</v>
       </c>
       <c r="E8">
-        <v>2.7140644875523599</v>
+        <v>2.71406448755236</v>
       </c>
       <c r="F8">
-        <v>36431.565890655504</v>
+        <v>36431.5658906555</v>
       </c>
       <c r="G8">
         <v>45.247946285329</v>
       </c>
       <c r="H8">
-        <v>42.999564251930401</v>
+        <v>42.9995642519304</v>
       </c>
       <c r="I8">
-        <v>28.941429045653202</v>
+        <v>28.9414290456532</v>
       </c>
       <c r="J8">
         <v>1.67512449608723</v>
       </c>
       <c r="K8">
-        <v>5.3727074482827204</v>
+        <v>5.37270744828272</v>
       </c>
       <c r="L8">
-        <v>-2.4365814296350301</v>
+        <v>-2.43658142963503</v>
       </c>
       <c r="M8">
-        <v>0.59550577402114901</v>
+        <v>0.595505774021149</v>
       </c>
       <c r="N8">
-        <v>22.660394725779899</v>
+        <v>22.6603947257799</v>
       </c>
       <c r="O8">
-        <v>57.869277529267301</v>
+        <v>57.8692775292673</v>
       </c>
       <c r="P8">
-        <v>65.400000000000006</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
       <c r="B9">
-        <v>1.4560017585754399</v>
+        <v>1.45600175857544</v>
       </c>
       <c r="C9">
         <v>-0.328279950461903</v>
@@ -855,13 +830,13 @@
         <v>28.8585344688926</v>
       </c>
       <c r="E9">
-        <v>2.5304818835106602</v>
+        <v>2.53048188351066</v>
       </c>
       <c r="F9">
-        <v>41486.190782878701</v>
+        <v>41486.1907828787</v>
       </c>
       <c r="G9">
-        <v>44.911153513771801</v>
+        <v>44.9111535137718</v>
       </c>
       <c r="H9">
         <v>42.4848634559389</v>
@@ -876,13 +851,13 @@
         <v>5.47711848457112</v>
       </c>
       <c r="L9">
-        <v>-2.5626506707368302</v>
+        <v>-2.56265067073683</v>
       </c>
       <c r="M9">
-        <v>0.56300079822540305</v>
+        <v>0.5630007982254031</v>
       </c>
       <c r="N9">
-        <v>22.219209760705599</v>
+        <v>22.2192097607056</v>
       </c>
       <c r="O9">
         <v>58.1525611309659</v>
@@ -891,57 +866,57 @@
         <v>65.5</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
       <c r="B10">
-        <v>1.3950347900390601</v>
+        <v>1.39503479003906</v>
       </c>
       <c r="C10">
-        <v>-0.96224494507722502</v>
+        <v>-0.962244945077225</v>
       </c>
       <c r="D10">
-        <v>29.199059678250201</v>
+        <v>29.1990596782502</v>
       </c>
       <c r="E10">
         <v>0.380171435849121</v>
       </c>
       <c r="F10">
-        <v>45464.818138515802</v>
+        <v>45464.8181385158</v>
       </c>
       <c r="G10">
         <v>45.2341073217247</v>
       </c>
       <c r="H10">
-        <v>42.450905897121501</v>
+        <v>42.4509058971215</v>
       </c>
       <c r="I10">
-        <v>29.980733162924601</v>
+        <v>29.9807331629246</v>
       </c>
       <c r="J10">
-        <v>2.8128619491478699</v>
+        <v>2.81286194914787</v>
       </c>
       <c r="K10">
-        <v>5.6982958336453198</v>
+        <v>5.69829583364532</v>
       </c>
       <c r="L10">
-        <v>-2.9929300994367001</v>
+        <v>-2.9929300994367</v>
       </c>
       <c r="M10">
-        <v>0.54375916719436601</v>
+        <v>0.543759167194366</v>
       </c>
       <c r="N10">
-        <v>22.089184234550402</v>
+        <v>22.0891842345504</v>
       </c>
       <c r="O10">
-        <v>59.179792841174802</v>
+        <v>59.1797928411748</v>
       </c>
       <c r="P10">
         <v>69.8</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
@@ -952,31 +927,31 @@
         <v>-0.81848014778611</v>
       </c>
       <c r="D11">
-        <v>25.880948231160801</v>
+        <v>25.8809482311608</v>
       </c>
       <c r="E11">
-        <v>-2.8245515371478298</v>
+        <v>-2.82455153714783</v>
       </c>
       <c r="F11">
         <v>41728.0884164132</v>
       </c>
       <c r="G11">
-        <v>48.405932473145199</v>
+        <v>48.4059324731452</v>
       </c>
       <c r="H11">
-        <v>41.819846493527699</v>
+        <v>41.8198464935277</v>
       </c>
       <c r="I11">
-        <v>26.318164071600499</v>
+        <v>26.3181640716005</v>
       </c>
       <c r="J11">
-        <v>8.7620478157448597E-2</v>
+        <v>0.0876204781574486</v>
       </c>
       <c r="K11">
-        <v>4.8799678569656297</v>
+        <v>4.87996785696563</v>
       </c>
       <c r="L11">
-        <v>-7.0447240428212998</v>
+        <v>-7.0447240428213</v>
       </c>
       <c r="M11">
         <v>0.512012898921967</v>
@@ -988,160 +963,160 @@
         <v>52.1991123027613</v>
       </c>
       <c r="P11">
-        <v>84.1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+        <v>84.09999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
       <c r="B12">
-        <v>1.4877561330795299</v>
+        <v>1.48775613307953</v>
       </c>
       <c r="C12">
         <v>-0.832545468638349</v>
       </c>
       <c r="D12">
-        <v>27.826488091555301</v>
+        <v>27.8264880915553</v>
       </c>
       <c r="E12">
-        <v>2.0003247603905101</v>
+        <v>2.00032476039051</v>
       </c>
       <c r="F12">
-        <v>40694.821169702504</v>
+        <v>40694.8211697025</v>
       </c>
       <c r="G12">
-        <v>49.692529103739602</v>
+        <v>49.6925291037396</v>
       </c>
       <c r="H12">
-        <v>43.265676727293503</v>
+        <v>43.2656767272935</v>
       </c>
       <c r="I12">
-        <v>28.761067156240799</v>
+        <v>28.7610671562408</v>
       </c>
       <c r="J12">
-        <v>1.5311227042092701</v>
+        <v>1.53112270420927</v>
       </c>
       <c r="K12">
-        <v>4.9433703108437701</v>
+        <v>4.94337031084377</v>
       </c>
       <c r="L12">
-        <v>-7.0449653923341904</v>
+        <v>-7.04496539233419</v>
       </c>
       <c r="M12">
-        <v>0.68108755350112904</v>
+        <v>0.681087553501129</v>
       </c>
       <c r="N12">
-        <v>21.986026477661099</v>
+        <v>21.9860264776611</v>
       </c>
       <c r="O12">
-        <v>56.587555247795997</v>
+        <v>56.587555247796</v>
       </c>
       <c r="P12">
         <v>86.3</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
       <c r="B13">
-        <v>1.5377732515335101</v>
+        <v>1.53777325153351</v>
       </c>
       <c r="C13">
         <v>-1.02802797917579</v>
       </c>
       <c r="D13">
-        <v>29.538847336075001</v>
+        <v>29.538847336075</v>
       </c>
       <c r="E13">
-        <v>2.4375765372900702</v>
+        <v>2.43757653729007</v>
       </c>
       <c r="F13">
-        <v>43929.784087381202</v>
+        <v>43929.7840873812</v>
       </c>
       <c r="G13">
-        <v>47.927974289250997</v>
+        <v>47.927974289251</v>
       </c>
       <c r="H13">
-        <v>42.969133930389098</v>
+        <v>42.9691339303891</v>
       </c>
       <c r="I13">
-        <v>31.066788145565599</v>
+        <v>31.0667881455656</v>
       </c>
       <c r="J13">
-        <v>2.1115979517499901</v>
+        <v>2.11159795174999</v>
       </c>
       <c r="K13">
-        <v>5.3931905798657302</v>
+        <v>5.39319057986573</v>
       </c>
       <c r="L13">
-        <v>-5.2326043209258097</v>
+        <v>-5.23260432092581</v>
       </c>
       <c r="M13">
-        <v>0.60299283266067505</v>
+        <v>0.602992832660675</v>
       </c>
       <c r="N13">
-        <v>21.826025121264699</v>
+        <v>21.8260251212647</v>
       </c>
       <c r="O13">
-        <v>60.605635481640597</v>
+        <v>60.6056354816406</v>
       </c>
       <c r="P13">
         <v>88.7</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
       <c r="B14">
-        <v>1.4719694852828999</v>
+        <v>1.4719694852829</v>
       </c>
       <c r="C14">
         <v>-1.22530807843013</v>
       </c>
       <c r="D14">
-        <v>30.355678652744398</v>
+        <v>30.3556786527444</v>
       </c>
       <c r="E14">
         <v>0.183835264973013</v>
       </c>
       <c r="F14">
-        <v>40863.581441233298</v>
+        <v>40863.5814412333</v>
       </c>
       <c r="G14">
-        <v>48.537171644104198</v>
+        <v>48.5371716441042</v>
       </c>
       <c r="H14">
-        <v>43.879080396384303</v>
+        <v>43.8790803963843</v>
       </c>
       <c r="I14">
         <v>31.3032784243658</v>
       </c>
       <c r="J14">
-        <v>1.9541953161350101</v>
+        <v>1.95419531613501</v>
       </c>
       <c r="K14">
-        <v>5.1544832538193504</v>
+        <v>5.15448325381935</v>
       </c>
       <c r="L14">
-        <v>-4.9460162725740702</v>
+        <v>-4.94601627257407</v>
       </c>
       <c r="M14">
-        <v>0.55494153499603305</v>
+        <v>0.554941534996033</v>
       </c>
       <c r="N14">
-        <v>22.608974141337999</v>
+        <v>22.608974141338</v>
       </c>
       <c r="O14">
-        <v>61.658957077110202</v>
+        <v>61.6589570771102</v>
       </c>
       <c r="P14">
         <v>91.7</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
@@ -1149,40 +1124,40 @@
         <v>1.30433368682861</v>
       </c>
       <c r="C15">
-        <v>-0.59799045690811004</v>
+        <v>-0.59799045690811</v>
       </c>
       <c r="D15">
-        <v>30.591285342777301</v>
+        <v>30.5912853427773</v>
       </c>
       <c r="E15">
-        <v>0.78175644623100005</v>
+        <v>0.781756446231</v>
       </c>
       <c r="F15">
-        <v>42669.179511189301</v>
+        <v>42669.1795111893</v>
       </c>
       <c r="G15">
-        <v>49.071731913933696</v>
+        <v>49.0717319139337</v>
       </c>
       <c r="H15">
-        <v>44.726457905407102</v>
+        <v>44.7264579054071</v>
       </c>
       <c r="I15">
         <v>31.2279485306189</v>
       </c>
       <c r="J15">
-        <v>0.86371549786187296</v>
+        <v>0.863715497861873</v>
       </c>
       <c r="K15">
-        <v>4.5254203438484097</v>
+        <v>4.52542034384841</v>
       </c>
       <c r="L15">
-        <v>-4.5478677383692796</v>
+        <v>-4.54786773836928</v>
       </c>
       <c r="M15">
-        <v>0.44874411821365401</v>
+        <v>0.448744118213654</v>
       </c>
       <c r="N15">
-        <v>23.204101168301399</v>
+        <v>23.2041011683014</v>
       </c>
       <c r="O15">
         <v>61.8192338733962</v>
@@ -1191,7 +1166,7 @@
         <v>94.5</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
@@ -1199,49 +1174,49 @@
         <v>1.2879855632782</v>
       </c>
       <c r="C16">
-        <v>-0.96273369938115105</v>
+        <v>-0.9627336993811511</v>
       </c>
       <c r="D16">
-        <v>30.741812901515001</v>
+        <v>30.741812901515</v>
       </c>
       <c r="E16">
-        <v>0.99783294729525096</v>
+        <v>0.997832947295251</v>
       </c>
       <c r="F16">
-        <v>43148.045928841602</v>
+        <v>43148.0459288416</v>
       </c>
       <c r="G16">
         <v>49.1207847434763</v>
       </c>
       <c r="H16">
-        <v>44.932480259508502</v>
+        <v>44.9324802595085</v>
       </c>
       <c r="I16">
         <v>31.4574540364356</v>
       </c>
       <c r="J16">
-        <v>0.50775882293796304</v>
+        <v>0.507758822937963</v>
       </c>
       <c r="K16">
-        <v>4.3167198302043603</v>
+        <v>4.31671983020436</v>
       </c>
       <c r="L16">
-        <v>-4.3098190764677398</v>
+        <v>-4.30981907646774</v>
       </c>
       <c r="M16">
-        <v>0.30056849122047402</v>
+        <v>0.300568491220474</v>
       </c>
       <c r="N16">
-        <v>23.155659352591101</v>
+        <v>23.1556593525911</v>
       </c>
       <c r="O16">
-        <v>62.199266937950703</v>
+        <v>62.1992669379507</v>
       </c>
       <c r="P16">
-        <v>96.1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+        <v>96.09999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
@@ -1249,99 +1224,99 @@
         <v>1.24783480167389</v>
       </c>
       <c r="C17">
-        <v>-0.33452843703290902</v>
+        <v>-0.334528437032909</v>
       </c>
       <c r="D17">
-        <v>31.693494726268899</v>
+        <v>31.6934947262689</v>
       </c>
       <c r="E17">
         <v>1.06675474783462</v>
       </c>
       <c r="F17">
-        <v>36702.432373337899</v>
+        <v>36702.4323733379</v>
       </c>
       <c r="G17">
-        <v>48.449188008221697</v>
+        <v>48.4491880082217</v>
       </c>
       <c r="H17">
-        <v>44.653006520936501</v>
+        <v>44.6530065209365</v>
       </c>
       <c r="I17">
-        <v>31.811192469379499</v>
+        <v>31.8111924693795</v>
       </c>
       <c r="J17">
-        <v>3.7514380512529803E-2</v>
+        <v>0.0375143805125298</v>
       </c>
       <c r="K17">
-        <v>4.0588013139799202</v>
+        <v>4.05880131397992</v>
       </c>
       <c r="L17">
         <v>-3.87230571650352</v>
       </c>
       <c r="M17">
-        <v>9.7759805619716603E-2</v>
+        <v>0.0977598056197166</v>
       </c>
       <c r="N17">
         <v>23.2974119760792</v>
       </c>
       <c r="O17">
-        <v>63.504687195648401</v>
+        <v>63.5046871956484</v>
       </c>
       <c r="P17">
-        <v>96.9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+        <v>96.90000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
       <c r="B18">
-        <v>1.3282889127731301</v>
+        <v>1.32828891277313</v>
       </c>
       <c r="C18">
-        <v>-0.53863235188589398</v>
+        <v>-0.538632351885894</v>
       </c>
       <c r="D18">
-        <v>31.498210070062999</v>
+        <v>31.498210070063</v>
       </c>
       <c r="E18">
-        <v>0.86003107542403301</v>
+        <v>0.860031075424033</v>
       </c>
       <c r="F18">
-        <v>37024.215713366902</v>
+        <v>37024.2157133669</v>
       </c>
       <c r="G18">
-        <v>48.150042799165803</v>
+        <v>48.1500427991658</v>
       </c>
       <c r="H18">
-        <v>44.450984201587701</v>
+        <v>44.4509842015877</v>
       </c>
       <c r="I18">
-        <v>31.844546368272098</v>
+        <v>31.8445463682721</v>
       </c>
       <c r="J18">
-        <v>0.18333486112382899</v>
+        <v>0.183334861123829</v>
       </c>
       <c r="K18">
-        <v>3.8405787188963898</v>
+        <v>3.84057871889639</v>
       </c>
       <c r="L18">
-        <v>-3.8660479307642799</v>
+        <v>-3.86604793076428</v>
       </c>
       <c r="M18">
         <v>-0.106349594891071</v>
       </c>
       <c r="N18">
-        <v>23.146328340575302</v>
+        <v>23.1463283405753</v>
       </c>
       <c r="O18">
-        <v>63.342756438335101</v>
+        <v>63.3427564383351</v>
       </c>
       <c r="P18">
-        <v>98.1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+        <v>98.09999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
@@ -1349,149 +1324,149 @@
         <v>1.22452700138092</v>
       </c>
       <c r="C19">
-        <v>-0.47461518521566898</v>
+        <v>-0.474615185215669</v>
       </c>
       <c r="D19">
         <v>32.311834044929</v>
       </c>
       <c r="E19">
-        <v>2.0836148599739901</v>
+        <v>2.08361485997399</v>
       </c>
       <c r="F19">
         <v>38687.1626407164</v>
       </c>
       <c r="G19">
-        <v>48.466341621356001</v>
+        <v>48.466341621356</v>
       </c>
       <c r="H19">
-        <v>45.084875487660703</v>
+        <v>45.0848754876607</v>
       </c>
       <c r="I19">
-        <v>33.084014111042102</v>
+        <v>33.0840141110421</v>
       </c>
       <c r="J19">
-        <v>1.0322827506466701</v>
+        <v>1.03228275064667</v>
       </c>
       <c r="K19">
-        <v>3.5861552109280899</v>
+        <v>3.58615521092809</v>
       </c>
       <c r="L19">
-        <v>-3.4240244222525802</v>
+        <v>-3.42402442225258</v>
       </c>
       <c r="M19">
-        <v>0.26570153236389199</v>
+        <v>0.265701532363892</v>
       </c>
       <c r="N19">
         <v>23.7863349624871</v>
       </c>
       <c r="O19">
-        <v>65.395848155971095</v>
+        <v>65.39584815597109</v>
       </c>
       <c r="P19">
         <v>98.7</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
       <c r="B20">
-        <v>1.2815515995025599</v>
+        <v>1.28155159950256</v>
       </c>
       <c r="C20">
-        <v>-0.73567061525537103</v>
+        <v>-0.735670615255371</v>
       </c>
       <c r="D20">
-        <v>32.917981892216403</v>
+        <v>32.9179818922164</v>
       </c>
       <c r="E20">
-        <v>1.6459087239588699</v>
+        <v>1.64590872395887</v>
       </c>
       <c r="F20">
-        <v>41418.176648484397</v>
+        <v>41418.1766484844</v>
       </c>
       <c r="G20">
-        <v>47.100077321421601</v>
+        <v>47.1000773214216</v>
       </c>
       <c r="H20">
-        <v>44.725937762114597</v>
+        <v>44.7259377621146</v>
       </c>
       <c r="I20">
-        <v>33.884278889010197</v>
+        <v>33.8842788890102</v>
       </c>
       <c r="J20">
-        <v>1.8508150831550101</v>
+        <v>1.85081508315501</v>
       </c>
       <c r="K20">
-        <v>3.6411314198942302</v>
+        <v>3.64113141989423</v>
       </c>
       <c r="L20">
-        <v>-2.3942044087645402</v>
+        <v>-2.39420440876454</v>
       </c>
       <c r="M20">
-        <v>1.3894104398787001E-2</v>
+        <v>0.013894104398787</v>
       </c>
       <c r="N20">
         <v>24.3098642807809</v>
       </c>
       <c r="O20">
-        <v>66.802260781226593</v>
+        <v>66.80226078122659</v>
       </c>
       <c r="P20">
         <v>98.5</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
       <c r="B21">
-        <v>1.2480622529983501</v>
+        <v>1.24806225299835</v>
       </c>
       <c r="C21">
-        <v>0.58736276457574799</v>
+        <v>0.587362764575748</v>
       </c>
       <c r="D21">
-        <v>32.889559391084703</v>
+        <v>32.8895593910847</v>
       </c>
       <c r="E21">
-        <v>2.0274464641923702</v>
+        <v>2.02744646419237</v>
       </c>
       <c r="F21">
-        <v>40408.284857475097</v>
+        <v>40408.2848574751</v>
       </c>
       <c r="G21">
         <v>45.8897902925031</v>
       </c>
       <c r="H21">
-        <v>43.655013216803802</v>
+        <v>43.6550132168038</v>
       </c>
       <c r="I21">
-        <v>33.539417783060202</v>
+        <v>33.5394177830602</v>
       </c>
       <c r="J21">
-        <v>1.1082549228829199</v>
+        <v>1.10825492288292</v>
       </c>
       <c r="K21">
-        <v>3.1651200491410298</v>
+        <v>3.16512004914103</v>
       </c>
       <c r="L21">
-        <v>-2.2893489155609599</v>
+        <v>-2.28934891556096</v>
       </c>
       <c r="M21">
-        <v>0.27134123444557201</v>
+        <v>0.271341234445572</v>
       </c>
       <c r="N21">
         <v>24.6605263993177</v>
       </c>
       <c r="O21">
-        <v>66.428977174144904</v>
+        <v>66.4289771741449</v>
       </c>
       <c r="P21">
-        <v>98.1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+        <v>98.09999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
@@ -1499,208 +1474,207 @@
         <v>1.12261998653412</v>
       </c>
       <c r="C22">
-        <v>-2.0031361365768601</v>
+        <v>-2.00313613657686</v>
       </c>
       <c r="D22">
-        <v>28.557222819265501</v>
+        <v>28.5572228192655</v>
       </c>
       <c r="E22">
-        <v>-7.4406458994823099</v>
+        <v>-7.44064589948231</v>
       </c>
       <c r="F22">
         <v>39169.8606000707</v>
       </c>
       <c r="G22">
-        <v>51.963631425798198</v>
+        <v>51.9636314257982</v>
       </c>
       <c r="H22">
-        <v>43.321990710166503</v>
+        <v>43.3219907101665</v>
       </c>
       <c r="I22">
-        <v>30.281667904799299</v>
+        <v>30.2816679047993</v>
       </c>
       <c r="J22">
-        <v>0.47649885272501402</v>
+        <v>0.476498852725014</v>
       </c>
       <c r="K22">
-        <v>2.3636534940757201</v>
+        <v>2.36365349407572</v>
       </c>
       <c r="L22">
-        <v>-8.7662591713618898</v>
+        <v>-8.76625917136189</v>
       </c>
       <c r="M22">
-        <v>0.28099283576011702</v>
+        <v>0.280992835760117</v>
       </c>
       <c r="N22">
-        <v>24.788806441613801</v>
+        <v>24.7888064416138</v>
       </c>
       <c r="O22">
-        <v>58.838890724064697</v>
+        <v>58.8388907240647</v>
       </c>
       <c r="P22">
         <v>114.9</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
       <c r="B23">
-        <v>1.2819362878799401</v>
+        <v>1.28193628787994</v>
       </c>
       <c r="C23">
-        <v>0.24423851178054201</v>
+        <v>0.244238511780542</v>
       </c>
       <c r="D23">
-        <v>31.288049933210502</v>
+        <v>31.2880499332105</v>
       </c>
       <c r="E23">
-        <v>6.8823378336023904</v>
+        <v>6.88233783360239</v>
       </c>
       <c r="F23">
-        <v>43725.099952124503</v>
+        <v>43725.0999521245</v>
       </c>
       <c r="G23">
-        <v>49.994444006530401</v>
+        <v>49.9944440065304</v>
       </c>
       <c r="H23">
-        <v>43.504848267154003</v>
+        <v>43.504848267154</v>
       </c>
       <c r="I23">
-        <v>32.500432697661502</v>
+        <v>32.5004326976615</v>
       </c>
       <c r="J23">
-        <v>1.6423314103839299</v>
+        <v>1.64233141038393</v>
       </c>
       <c r="K23">
-        <v>2.6773015454515998</v>
+        <v>2.6773015454516</v>
       </c>
       <c r="L23">
-        <v>-6.5490789590201297</v>
+        <v>-6.54907895902013</v>
       </c>
       <c r="M23">
-        <v>0.32561236619949302</v>
+        <v>0.325612366199493</v>
       </c>
       <c r="N23">
         <v>23.9794445386059</v>
       </c>
       <c r="O23">
-        <v>63.788482630871997</v>
+        <v>63.788482630872</v>
       </c>
       <c r="P23">
         <v>112.8</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
       <c r="B24">
-        <v>1.2594361305236801</v>
+        <v>1.25943613052368</v>
       </c>
       <c r="C24">
         <v>-1.43157299945545</v>
       </c>
       <c r="D24">
-        <v>36.503668890407802</v>
+        <v>36.5036688904078</v>
       </c>
       <c r="E24">
-        <v>2.5708404756779299</v>
+        <v>2.57084047567793</v>
       </c>
       <c r="F24">
-        <v>41082.811932074699</v>
+        <v>41082.8119320747</v>
       </c>
       <c r="G24">
-        <v>48.833867144177901</v>
+        <v>48.8338671441779</v>
       </c>
       <c r="H24">
-        <v>44.255016598033798</v>
+        <v>44.2550165980338</v>
       </c>
       <c r="I24">
-        <v>39.286474720714303</v>
+        <v>39.2864747207143</v>
       </c>
       <c r="J24">
-        <v>5.2223674836973597</v>
+        <v>5.22236748369736</v>
       </c>
       <c r="K24">
-        <v>3.7618615623840399</v>
+        <v>3.76186156238404</v>
       </c>
       <c r="L24">
-        <v>-4.6968613428684902</v>
+        <v>-4.69686134286849</v>
       </c>
       <c r="M24">
-        <v>0.39333921670913702</v>
+        <v>0.393339216709137</v>
       </c>
       <c r="N24">
-        <v>24.534247684465999</v>
+        <v>24.534247684466</v>
       </c>
       <c r="O24">
-        <v>75.790143611122105</v>
+        <v>75.7901436111221</v>
       </c>
       <c r="P24">
         <v>111.4</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
       <c r="B25">
-        <v>1.1848218441009499</v>
+        <v>1.18482184410095</v>
       </c>
       <c r="C25">
         <v>-1.04452732139601</v>
       </c>
       <c r="D25">
-        <v>34.280030580474197</v>
+        <v>34.2800305804742</v>
       </c>
       <c r="E25">
-        <v>0.93648751885085302</v>
+        <v>0.936487518850853</v>
       </c>
       <c r="F25">
-        <v>44690.934539511698</v>
+        <v>44690.9345395117</v>
       </c>
       <c r="G25">
         <v>47.3264654106394</v>
       </c>
       <c r="H25">
-        <v>42.274986460366797</v>
+        <v>42.2749864603668</v>
       </c>
       <c r="I25">
-        <v>36.279524212718997</v>
+        <v>36.279524212719</v>
       </c>
       <c r="J25">
-        <v>4.8783572650843796</v>
+        <v>4.87835726508438</v>
       </c>
       <c r="K25">
         <v>3.37281623755023</v>
       </c>
       <c r="L25">
-        <v>-5.1343748806446703</v>
+        <v>-5.13437488064467</v>
       </c>
       <c r="M25">
-        <v>0.34369796514511097</v>
+        <v>0.343697965145111</v>
       </c>
       <c r="N25">
         <v>23.1103805885841</v>
       </c>
       <c r="O25">
-        <v>70.559554793193101</v>
+        <v>70.5595547931931</v>
       </c>
       <c r="P25">
         <v>109.6</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
-      <c r="B26" s="2"/>
       <c r="C26">
-        <v>8.5083932569125595E-2</v>
+        <v>0.08508393256912559</v>
       </c>
       <c r="D26">
-        <v>33.244084247212299</v>
+        <v>33.2440842472123</v>
       </c>
       <c r="E26">
         <v>1.16613851497229</v>
@@ -1708,22 +1682,17 @@
       <c r="F26">
         <v>46150.4876861593</v>
       </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
       <c r="I26">
-        <v>33.978886509597899</v>
+        <v>33.9788865095979</v>
       </c>
       <c r="J26">
-        <v>1.9990494229146401</v>
-      </c>
-      <c r="K26" s="2"/>
+        <v>1.99904942291464</v>
+      </c>
       <c r="L26">
         <v>-5.8</v>
       </c>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
       <c r="O26">
-        <v>67.222970756810099</v>
+        <v>67.2229707568101</v>
       </c>
       <c r="P26">
         <v>113.1</v>
